--- a/LOV3_HTX_H1_2026_YTD_PL.xlsx
+++ b/LOV3_HTX_H1_2026_YTD_PL.xlsx
@@ -2092,13 +2092,13 @@
         <v>23989.32</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>11377.89</v>
+        <v>5877.89</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>56188.56</v>
+        <v>50688.56</v>
       </c>
       <c r="I64" s="10" t="n">
-        <v>0.01521778743478883</v>
+        <v>0.01372819896889224</v>
       </c>
     </row>
     <row r="65">
@@ -2309,13 +2309,13 @@
         <v>70250.84</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>91621.53</v>
+        <v>86121.53</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>273827.64</v>
+        <v>268327.64</v>
       </c>
       <c r="I71" s="13" t="n">
-        <v>0.07416190803412438</v>
+        <v>0.07267231956822778</v>
       </c>
     </row>
     <row r="73">
@@ -2386,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>6221.75</v>
+        <v>11721.75</v>
       </c>
       <c r="I75" s="10" t="n">
-        <v>0.001685063097762203</v>
+        <v>0.003174651563658794</v>
       </c>
     </row>
     <row r="76">
@@ -2448,13 +2448,13 @@
         <v>2342.9</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>3450</v>
+        <v>8950</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>19777.18</v>
+        <v>25277.18</v>
       </c>
       <c r="I77" s="13" t="n">
-        <v>0.00535633803926559</v>
+        <v>0.006845926505162182</v>
       </c>
     </row>
     <row r="79">
